--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1024_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1024_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,16 @@
           <t>Grandfather Clocks</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impatient Billionaire</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Dont Look</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -471,6 +481,12 @@
       <c r="E2" t="n">
         <v>0.2669128179550171</v>
       </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -488,6 +504,12 @@
       <c r="E3" t="n">
         <v>0.4066035449504852</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -505,6 +527,12 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -522,6 +550,12 @@
       <c r="E5" t="n">
         <v>0.6962018013000488</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -539,6 +573,12 @@
       <c r="E6" t="n">
         <v>0.37120720744133</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -556,6 +596,12 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -573,6 +619,12 @@
       <c r="E8" t="n">
         <v>0.5864349603652954</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -590,6 +642,12 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -607,6 +665,12 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -624,6 +688,12 @@
       <c r="E11" t="n">
         <v>0.653889000415802</v>
       </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -641,6 +711,12 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -658,6 +734,12 @@
       <c r="E13" t="n">
         <v>0.5256655812263489</v>
       </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -675,6 +757,12 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -692,6 +780,12 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -709,6 +803,12 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -726,6 +826,12 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -743,6 +849,12 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -760,6 +872,10 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -777,6 +893,10 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -794,6 +914,10 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -809,6 +933,10 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -824,6 +952,10 @@
       <c r="E23" t="n">
         <v>0.07847748696804047</v>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -839,6 +971,10 @@
       <c r="E24" t="n">
         <v>0.5653286576271057</v>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -851,6 +987,10 @@
       </c>
       <c r="E25" t="n">
         <v>0.6612663269042969</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -865,6 +1005,10 @@
       <c r="E26" t="n">
         <v>0.4879348874092102</v>
       </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -877,6 +1021,10 @@
       </c>
       <c r="E27" t="n">
         <v>0.2070222645998001</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -891,6 +1039,10 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -904,6 +1056,10 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -917,6 +1073,10 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -928,6 +1088,10 @@
         <v>0.1397000551223755</v>
       </c>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -939,6 +1103,10 @@
         <v>0</v>
       </c>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -950,6 +1118,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -961,6 +1133,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -972,6 +1148,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -983,6 +1163,10 @@
         <v>0.4067534804344177</v>
       </c>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -994,6 +1178,10 @@
         <v>0.3386609852313995</v>
       </c>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1005,6 +1193,10 @@
         <v>0.1744940578937531</v>
       </c>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1016,6 +1208,10 @@
         <v>0.1435827910900116</v>
       </c>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1027,6 +1223,10 @@
         <v>0.1790715008974075</v>
       </c>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1038,6 +1238,10 @@
         <v>0.4347766637802124</v>
       </c>
       <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1049,6 +1253,10 @@
         <v>0</v>
       </c>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1060,6 +1268,8 @@
         <v>0</v>
       </c>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1071,6 +1281,8 @@
         <v>0.2385123819112778</v>
       </c>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1082,6 +1294,8 @@
         <v>0</v>
       </c>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1093,6 +1307,8 @@
         <v>0</v>
       </c>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1104,6 +1320,8 @@
         <v>0</v>
       </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1115,6 +1333,8 @@
         <v>0</v>
       </c>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1126,6 +1346,8 @@
         <v>0</v>
       </c>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1137,6 +1359,8 @@
         <v>0.3008210062980652</v>
       </c>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1148,6 +1372,8 @@
         <v>0</v>
       </c>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1159,6 +1385,8 @@
         <v>0.4406366050243378</v>
       </c>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1170,6 +1398,8 @@
         <v>0.5065648555755615</v>
       </c>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1181,6 +1411,8 @@
         <v>0</v>
       </c>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1192,6 +1424,8 @@
         <v>0</v>
       </c>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1203,6 +1437,8 @@
         <v>0.3103120625019073</v>
       </c>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
